--- a/AAII_Financials/Quarterly/ROOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ROOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="92">
   <si>
     <t>ROOT</t>
   </si>
@@ -656,131 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
@@ -793,92 +794,95 @@
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>389200</v>
+      </c>
+      <c r="E8" s="3">
         <v>393500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>397000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>387800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>382900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>349400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>326700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>305700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>289200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>254900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>194800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>115300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>80400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>85400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>93200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>93800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>89800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>68600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>50900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>50500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>245400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>290200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>104100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,53 +895,56 @@
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>239900</v>
+      </c>
+      <c r="E9" s="3">
         <v>226200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>245900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>239400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>233300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>205600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>191800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>184500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>190300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>166400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>122700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>85800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>59500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>63300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -989,53 +996,56 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E10" s="3">
         <v>167300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>151100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>148400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>149600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>143800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>134900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>121200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>98900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>88500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>72100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1097,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,68 +1336,71 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="D14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>5500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1900</v>
       </c>
       <c r="O14" s="3">
         <v>1900</v>
       </c>
       <c r="P14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q14" s="3">
         <v>5600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1396,8 +1416,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1417,53 +1437,56 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3">
         <v>3100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1500</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2700</v>
       </c>
       <c r="O15" s="3">
         <v>2700</v>
       </c>
       <c r="P15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,92 +1574,93 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>354600</v>
+      </c>
+      <c r="E17" s="3">
         <v>352600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>386500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>387500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>355500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>325700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>291700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>271300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>285400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>249400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>205300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>147400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>98100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>94300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>119000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>130800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>166700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>157400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>201000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>220700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>261900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>162900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>139400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>116200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>376500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>550300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>198500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,92 +1673,95 @@
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E18" s="3">
         <v>40900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>23700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-32100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-47700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-57100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-86300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-72000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-107800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-126900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-172100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-94300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-88500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-65700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-131100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-260100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-94400</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1744,8 +1774,11 @@
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,8 +1813,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1824,8 +1858,8 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1849,22 +1883,22 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>38600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>13700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>0</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
@@ -1878,92 +1912,95 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E21" s="3">
         <v>44000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>29300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>36500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-29400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-20600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-43400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-54200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-83300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-68400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-102200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-123100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-168400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-90800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-46400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-47000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-121600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-257000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-93900</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,19 +2013,22 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E22" s="3">
         <v>4800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5300</v>
       </c>
       <c r="G22" s="3">
         <v>5300</v>
@@ -1997,10 +2037,10 @@
         <v>5300</v>
       </c>
       <c r="I22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J22" s="3">
         <v>7400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>11600</v>
       </c>
       <c r="K22" s="3">
         <v>11600</v>
@@ -2009,59 +2049,59 @@
         <v>11600</v>
       </c>
       <c r="M22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N22" s="3">
         <v>11700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>83400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>33200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2074,92 +2114,95 @@
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>36100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-45800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-58300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-66400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-95500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-77500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-109900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-133000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-178600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2172,8 +2215,11 @@
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2181,14 +2227,14 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2216,8 +2262,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2270,8 +2316,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,92 +2417,95 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E26" s="3">
         <v>35900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-36700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-58300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-66400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-95500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-77500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-109900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-133000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-178600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,92 +2518,95 @@
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E27" s="3">
         <v>34200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-36700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-58300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-66400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-95500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-77500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-109900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-133000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-178600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,8 +2619,11 @@
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,8 +3023,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3000,8 +3070,8 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3025,22 +3095,22 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-38600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
@@ -3054,92 +3124,95 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E33" s="3">
         <v>34200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-36700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-58300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-66400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-95500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-77500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-109900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-133000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-178600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3225,11 @@
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,92 +3326,95 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E35" s="3">
         <v>34200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-36700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-58300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-66400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-95500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-77500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-109900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-133000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-178600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,97 +3427,100 @@
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3451,8 +3533,11 @@
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,86 +3609,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>509600</v>
+      </c>
+      <c r="E41" s="3">
         <v>597200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>669300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>653300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>641400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>609400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>599300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>674800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>667200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>640500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>678700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>635300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>628000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>679300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>762100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>819700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>885600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>934700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>706000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>834100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>973100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1106300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1112800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>217800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>240900</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3708,11 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,44 +3720,44 @@
         <v>10800</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>3500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3719,86 +3809,89 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>330700</v>
+      </c>
+      <c r="E43" s="3">
         <v>350800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>332800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>352500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>341300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>360700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>305300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>308700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>296000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>292000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>247100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>187900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>127600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>113500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>129900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>132200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>157100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>148100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>175800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>160200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>161000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>130100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>138400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>130100</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3817,8 +3910,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3861,8 +3957,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3915,86 +4011,89 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E45" s="3">
         <v>122100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>129800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>142300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>145500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>157800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>150600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>160600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>180200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>147100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>125300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>137700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>130200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>129400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>74200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>86200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>91800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>106700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>114700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>111500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>101300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>112800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>119100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40800</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4013,53 +4112,56 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1028500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1092600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1158800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1160900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1147700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1157700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1096100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1191500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1204500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1139500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1101200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1000600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>963200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>997400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4111,86 +4213,89 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>510800</v>
+      </c>
+      <c r="E47" s="3">
         <v>460700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>391400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>362200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>323600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>317300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>296400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>270600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>228200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>211700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>170300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>168900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>164400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>130800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>132800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>124100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>124700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>133500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>134600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>132100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>135200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>136800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>221500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>222000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>215200</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,52 +4314,55 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>3200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>4400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>6300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -4262,33 +4370,33 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3">
         <v>5100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4307,20 +4415,23 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E49" s="3">
         <v>46500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>37800</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -4328,23 +4439,23 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>32200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26500</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>21400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>29400</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
@@ -4372,15 +4483,15 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3">
         <v>9600</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4507,8 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF49" s="3">
-        <v>0</v>
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG49" s="3">
         <v>0</v>
@@ -4405,8 +4516,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,86 +4718,89 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E52" s="3">
         <v>85100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>119300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>116400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>110500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>66600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>73300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>67300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>72900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1400</v>
       </c>
       <c r="R52" s="3">
         <v>1400</v>
       </c>
       <c r="S52" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="T52" s="3">
         <v>1500</v>
       </c>
       <c r="U52" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="V52" s="3">
         <v>1000</v>
       </c>
       <c r="W52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X52" s="3">
         <v>1300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>4000</v>
       </c>
       <c r="Y52" s="3">
         <v>4000</v>
       </c>
       <c r="Z52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8200</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4699,8 +4819,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,86 +4920,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1668500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1684900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1674500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1642400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1587700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1585500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1495700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1561900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1495800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1432300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1347700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1240200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1194900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1201100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1312900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1384200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1479800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1563200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1319300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1524500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1587700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1704200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1762300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>838500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>706800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4895,8 +5021,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,86 +5097,87 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E57" s="3">
         <v>138300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>76600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>68100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>83300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>110200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>110600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>95000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>120000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>119600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>128200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>111900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>40100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>23800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>70800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>61500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>29700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5065,8 +5196,11 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5074,11 +5208,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -5163,86 +5297,89 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E59" s="3">
         <v>412400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>393700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>409300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>395200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>420300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>353900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>354400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>339700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>339400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>283700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>218900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>154600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>141100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>551000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>568400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>604200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>632300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>616000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>615300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>552200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>521600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>483400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>556800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>406000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5261,53 +5398,56 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>519500</v>
+      </c>
+      <c r="E60" s="3">
         <v>550700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>472600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>479900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>463300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>503600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>457800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>464600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>450300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>434400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>403700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>338500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>282800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>253000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5359,86 +5499,89 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>197800</v>
+      </c>
+      <c r="E61" s="3">
         <v>200300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>202300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>200100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>200000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>206100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>300900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>299300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>307200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>298300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>297400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>296300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>288100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>287400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>286700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>285900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>201700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>197100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>192200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>188200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>220000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>190100</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5457,53 +5600,56 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>511300</v>
+      </c>
+      <c r="E62" s="3">
         <v>496000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>603300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>585100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>567800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>541200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>516100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>502500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>482100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>420900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>359100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>314300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>288300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>296100</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -5555,8 +5701,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,86 +6004,89 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1228600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1247000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1278200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1265400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1231200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1244800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1180000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1268000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1232500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1154600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1070000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>951100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>868500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>845400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>923800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>941300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>979800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>982500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>670900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>888500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>825700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>769900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>729900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>848500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>633600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5947,8 +6105,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6239,7 +6407,7 @@
         <v>112000</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>112000</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -6251,13 +6419,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>560400</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>560400</v>
       </c>
       <c r="AB70" s="3">
-        <v>0</v>
+        <v>560400</v>
       </c>
       <c r="AC70" s="3">
         <v>0</v>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,86 +6546,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1580300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1605700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1641600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1646900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1641500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1663500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1681900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1704000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1726800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1721400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1715200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1691200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1645400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1608700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1567800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1500400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1436400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1346500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1270100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1159200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1026200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-847600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-748000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-614700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-529500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6473,8 +6647,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,86 +6950,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E76" s="3">
         <v>325900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>284300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>265000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>244500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>228700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>203700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>181900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>151300</v>
-      </c>
-      <c r="L76" s="3">
-        <v>165700</v>
       </c>
       <c r="M76" s="3">
         <v>165700</v>
       </c>
       <c r="N76" s="3">
+        <v>165700</v>
+      </c>
+      <c r="O76" s="3">
         <v>177100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>214400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>243700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>277100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>330900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>388000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>468700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>536400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>636000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>762000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>934300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1032400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-570400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-487200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6865,8 +7051,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,97 +7152,100 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7066,92 +7258,95 @@
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E81" s="3">
         <v>34200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-36700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-58300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-66400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-95500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-77500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-109900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-133000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-178600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-99600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-133300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-85200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-282400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-97000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7164,8 +7359,11 @@
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,92 +7398,93 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-2100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2700</v>
       </c>
       <c r="K83" s="3">
         <v>2700</v>
       </c>
       <c r="L83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>3500</v>
       </c>
       <c r="Y83" s="3">
         <v>3500</v>
       </c>
       <c r="Z83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AA83" s="3">
         <v>5000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>3100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>500</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7298,8 +7497,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,92 +8002,95 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E89" s="3">
         <v>9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>52000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>26800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>69200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>62600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-83700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-46700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-59000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-53700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-51200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-39100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-137800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-135600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-90900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-192400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-62400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-127200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-38000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7886,8 +8103,11 @@
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,8 +8142,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7942,72 +8163,72 @@
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8020,8 +8241,11 @@
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,92 +8443,95 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-32500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>81300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-99300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-45600</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8314,8 +8544,11 @@
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,8 +8583,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8394,8 +8628,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8448,8 +8682,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,92 +8985,95 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-104400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-3000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>286200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-82600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1098400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>13100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>535500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>92700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8840,8 +9086,11 @@
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8884,8 +9133,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8938,92 +9187,95 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-81000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-75500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-51300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-82800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-57600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-65900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-49100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>228700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-128100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-139000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-133200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>895000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-174700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>294300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>9100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9034,6 +9286,9 @@
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
